--- a/261/food/tm2026-sm.xlsx
+++ b/261/food/tm2026-sm.xlsx
@@ -1193,7 +1193,7 @@
       </c>
       <c r="C1" s="79" t="inlineStr">
         <is>
-          <t>ГБОУ С(к)ОШИ для детей с ЗПР</t>
+          <t xml:space="preserve">ГБОУ С(к)ОШИ для детей с ЗПР </t>
         </is>
       </c>
       <c r="D1" s="80" t="n"/>
